--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/LOUISIANA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/LOUISIANA_2020.xlsx
@@ -427,7 +427,7 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="5">
@@ -571,7 +571,7 @@
         <v>2</v>
       </c>
       <c r="D12">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="13">
@@ -643,7 +643,7 @@
         <v>2</v>
       </c>
       <c r="D16">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="17">
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="19">
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="24">
@@ -787,7 +787,7 @@
         <v>2</v>
       </c>
       <c r="D24">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="25">
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="D25">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="26">
@@ -841,7 +841,7 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="28">
@@ -877,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="30">
@@ -913,7 +913,7 @@
         <v>2</v>
       </c>
       <c r="D31">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="32">
@@ -967,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="D34">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="35">
@@ -1075,7 +1075,7 @@
         <v>2</v>
       </c>
       <c r="D40">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="41">
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="D49">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="50">
@@ -1363,7 +1363,7 @@
         <v>2</v>
       </c>
       <c r="D56">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="57">
@@ -1417,7 +1417,7 @@
         <v>2</v>
       </c>
       <c r="D59">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="60">
@@ -1507,7 +1507,7 @@
         <v>2</v>
       </c>
       <c r="D64">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="65">
@@ -1597,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="D69">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="70">
@@ -1831,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="83">
@@ -1867,7 +1867,7 @@
         <v>2</v>
       </c>
       <c r="D84">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="85">
@@ -2227,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="D104">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="105">
@@ -2245,7 +2245,7 @@
         <v>2</v>
       </c>
       <c r="D105">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="106">
@@ -2299,7 +2299,7 @@
         <v>2</v>
       </c>
       <c r="D108">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="109">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C109">
@@ -2569,7 +2569,7 @@
         <v>2</v>
       </c>
       <c r="D123">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="124">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C128">
@@ -2821,7 +2821,7 @@
         <v>2</v>
       </c>
       <c r="D137">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="138">
@@ -2893,7 +2893,7 @@
         <v>2</v>
       </c>
       <c r="D141">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="142">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C142">
@@ -3001,7 +3001,7 @@
         <v>2</v>
       </c>
       <c r="D147">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="148">
@@ -3037,7 +3037,7 @@
         <v>2</v>
       </c>
       <c r="D149">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="150">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C150">
@@ -3109,7 +3109,7 @@
         <v>2</v>
       </c>
       <c r="D153">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="154">
@@ -3163,7 +3163,7 @@
         <v>2</v>
       </c>
       <c r="D156">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="157">
@@ -3199,7 +3199,7 @@
         <v>2</v>
       </c>
       <c r="D158">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="159">
@@ -3217,7 +3217,7 @@
         <v>2</v>
       </c>
       <c r="D159">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="160">
@@ -3325,7 +3325,7 @@
         <v>20</v>
       </c>
       <c r="D165">
-        <v>0.009708737864077669</v>
+        <v>0.009708737864077667</v>
       </c>
     </row>
     <row r="166">
@@ -3631,7 +3631,7 @@
         <v>2</v>
       </c>
       <c r="D182">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="183">
@@ -3811,7 +3811,7 @@
         <v>2</v>
       </c>
       <c r="D192">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="193">
@@ -3937,7 +3937,7 @@
         <v>2</v>
       </c>
       <c r="D199">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="200">
@@ -3955,7 +3955,7 @@
         <v>2</v>
       </c>
       <c r="D200">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="201">
@@ -3991,7 +3991,7 @@
         <v>2</v>
       </c>
       <c r="D202">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="203">
@@ -4063,7 +4063,7 @@
         <v>2</v>
       </c>
       <c r="D206">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="207">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C209">
@@ -4279,7 +4279,7 @@
         <v>2</v>
       </c>
       <c r="D218">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="219">
@@ -4423,7 +4423,7 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="227">
@@ -4531,7 +4531,7 @@
         <v>2</v>
       </c>
       <c r="D232">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="233">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C234">
@@ -4603,7 +4603,7 @@
         <v>2</v>
       </c>
       <c r="D236">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="237">
@@ -4621,7 +4621,7 @@
         <v>2</v>
       </c>
       <c r="D237">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="238">
@@ -4783,7 +4783,7 @@
         <v>2</v>
       </c>
       <c r="D246">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="247">
@@ -4963,7 +4963,7 @@
         <v>2</v>
       </c>
       <c r="D256">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="257">
@@ -4999,7 +4999,7 @@
         <v>2</v>
       </c>
       <c r="D258">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="259">
@@ -5017,7 +5017,7 @@
         <v>2</v>
       </c>
       <c r="D259">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="260">
@@ -5107,7 +5107,7 @@
         <v>2</v>
       </c>
       <c r="D264">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="265">
@@ -5161,7 +5161,7 @@
         <v>2</v>
       </c>
       <c r="D267">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="268">
@@ -5413,7 +5413,7 @@
         <v>2</v>
       </c>
       <c r="D281">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="282">
@@ -5485,7 +5485,7 @@
         <v>2</v>
       </c>
       <c r="D285">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="286">
@@ -5539,7 +5539,7 @@
         <v>2</v>
       </c>
       <c r="D288">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="289">
@@ -5593,7 +5593,7 @@
         <v>2</v>
       </c>
       <c r="D291">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="292">
@@ -5629,7 +5629,7 @@
         <v>2</v>
       </c>
       <c r="D293">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="294">
@@ -5755,7 +5755,7 @@
         <v>2</v>
       </c>
       <c r="D300">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="301">
@@ -5773,7 +5773,7 @@
         <v>2</v>
       </c>
       <c r="D301">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="302">
@@ -5845,7 +5845,7 @@
         <v>2</v>
       </c>
       <c r="D305">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="306">
@@ -5899,7 +5899,7 @@
         <v>2</v>
       </c>
       <c r="D308">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="309">
@@ -5989,7 +5989,7 @@
         <v>2</v>
       </c>
       <c r="D313">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="314">
@@ -6151,7 +6151,7 @@
         <v>2</v>
       </c>
       <c r="D322">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="323">
@@ -6169,7 +6169,7 @@
         <v>2</v>
       </c>
       <c r="D323">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="324">
@@ -6277,7 +6277,7 @@
         <v>2</v>
       </c>
       <c r="D329">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="330">
@@ -6295,7 +6295,7 @@
         <v>2</v>
       </c>
       <c r="D330">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="331">
@@ -6331,7 +6331,7 @@
         <v>2</v>
       </c>
       <c r="D332">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="333">
@@ -6349,7 +6349,7 @@
         <v>2</v>
       </c>
       <c r="D333">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="334">
@@ -6511,7 +6511,7 @@
         <v>2</v>
       </c>
       <c r="D342">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="343">
@@ -6601,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="D347">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="348">
@@ -6799,7 +6799,7 @@
         <v>2</v>
       </c>
       <c r="D358">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="359">
@@ -6835,7 +6835,7 @@
         <v>2</v>
       </c>
       <c r="D360">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="361">
@@ -6889,7 +6889,7 @@
         <v>2</v>
       </c>
       <c r="D363">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="364">
@@ -6943,7 +6943,7 @@
         <v>2</v>
       </c>
       <c r="D366">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="367">
@@ -6979,7 +6979,7 @@
         <v>2</v>
       </c>
       <c r="D368">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="369">
@@ -7087,7 +7087,7 @@
         <v>2</v>
       </c>
       <c r="D374">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="375">
@@ -7123,7 +7123,7 @@
         <v>2</v>
       </c>
       <c r="D376">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="377">
@@ -7141,7 +7141,7 @@
         <v>2</v>
       </c>
       <c r="D377">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="378">
@@ -7159,7 +7159,7 @@
         <v>2</v>
       </c>
       <c r="D378">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="379">
@@ -7177,7 +7177,7 @@
         <v>2</v>
       </c>
       <c r="D379">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="380">
@@ -7321,7 +7321,7 @@
         <v>2</v>
       </c>
       <c r="D387">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="388">
@@ -7393,7 +7393,7 @@
         <v>2</v>
       </c>
       <c r="D391">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="392">
@@ -7411,7 +7411,7 @@
         <v>2</v>
       </c>
       <c r="D392">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="393">
@@ -7591,7 +7591,7 @@
         <v>2</v>
       </c>
       <c r="D402">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="403">
@@ -7609,7 +7609,7 @@
         <v>2</v>
       </c>
       <c r="D403">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="404">
@@ -7663,7 +7663,7 @@
         <v>2</v>
       </c>
       <c r="D406">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="407">
@@ -7771,7 +7771,7 @@
         <v>2</v>
       </c>
       <c r="D412">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="413">
@@ -7879,7 +7879,7 @@
         <v>2</v>
       </c>
       <c r="D418">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="419">
@@ -7987,7 +7987,7 @@
         <v>2</v>
       </c>
       <c r="D424">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="425">
@@ -8023,7 +8023,7 @@
         <v>2</v>
       </c>
       <c r="D426">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="427">
@@ -8059,7 +8059,7 @@
         <v>2</v>
       </c>
       <c r="D428">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="429">
@@ -8113,7 +8113,7 @@
         <v>2</v>
       </c>
       <c r="D431">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="432">
@@ -8149,7 +8149,7 @@
         <v>2</v>
       </c>
       <c r="D433">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="434">
@@ -8239,7 +8239,7 @@
         <v>2</v>
       </c>
       <c r="D438">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="439">
@@ -8311,7 +8311,7 @@
         <v>2</v>
       </c>
       <c r="D442">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="443">
@@ -8347,7 +8347,7 @@
         <v>2</v>
       </c>
       <c r="D444">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="445">
@@ -8419,7 +8419,7 @@
         <v>2</v>
       </c>
       <c r="D448">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="449">
@@ -8473,7 +8473,7 @@
         <v>2</v>
       </c>
       <c r="D451">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="452">
@@ -8509,7 +8509,7 @@
         <v>2</v>
       </c>
       <c r="D453">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="454">
@@ -8527,7 +8527,7 @@
         <v>2</v>
       </c>
       <c r="D454">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="455">
@@ -8707,7 +8707,7 @@
         <v>2</v>
       </c>
       <c r="D464">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="465">
@@ -8851,7 +8851,7 @@
         <v>2</v>
       </c>
       <c r="D472">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="473">
@@ -8869,7 +8869,7 @@
         <v>2</v>
       </c>
       <c r="D473">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="474">
@@ -8959,7 +8959,7 @@
         <v>2</v>
       </c>
       <c r="D478">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="479">
@@ -8995,7 +8995,7 @@
         <v>2</v>
       </c>
       <c r="D480">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="481">
@@ -9211,7 +9211,7 @@
         <v>2</v>
       </c>
       <c r="D492">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="493">
@@ -9319,7 +9319,7 @@
         <v>2</v>
       </c>
       <c r="D498">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="499">
@@ -9499,7 +9499,7 @@
         <v>2</v>
       </c>
       <c r="D508">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="509">
@@ -9535,7 +9535,7 @@
         <v>2</v>
       </c>
       <c r="D510">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="511">
@@ -9553,7 +9553,7 @@
         <v>20</v>
       </c>
       <c r="D511">
-        <v>0.009708737864077669</v>
+        <v>0.009708737864077667</v>
       </c>
     </row>
     <row r="512">
@@ -9679,7 +9679,7 @@
         <v>2</v>
       </c>
       <c r="D518">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="519">
@@ -9697,7 +9697,7 @@
         <v>2</v>
       </c>
       <c r="D519">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="520">
@@ -9841,7 +9841,7 @@
         <v>2</v>
       </c>
       <c r="D527">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="528">
@@ -9895,7 +9895,7 @@
         <v>2</v>
       </c>
       <c r="D530">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="531">
@@ -10075,7 +10075,7 @@
         <v>2</v>
       </c>
       <c r="D540">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="541">
@@ -10201,7 +10201,7 @@
         <v>2</v>
       </c>
       <c r="D547">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="548">
@@ -10255,7 +10255,7 @@
         <v>2</v>
       </c>
       <c r="D550">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="551">
@@ -10273,7 +10273,7 @@
         <v>2</v>
       </c>
       <c r="D551">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="552">
@@ -10327,7 +10327,7 @@
         <v>2</v>
       </c>
       <c r="D554">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="555">
@@ -10381,7 +10381,7 @@
         <v>2</v>
       </c>
       <c r="D557">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="558">
@@ -10435,7 +10435,7 @@
         <v>2</v>
       </c>
       <c r="D560">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="561">
@@ -10453,7 +10453,7 @@
         <v>2</v>
       </c>
       <c r="D561">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="562">
@@ -10471,7 +10471,7 @@
         <v>2</v>
       </c>
       <c r="D562">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="563">
@@ -10579,7 +10579,7 @@
         <v>2</v>
       </c>
       <c r="D568">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="569">
@@ -10669,7 +10669,7 @@
         <v>2</v>
       </c>
       <c r="D573">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="574">
@@ -10741,7 +10741,7 @@
         <v>2</v>
       </c>
       <c r="D577">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="578">
@@ -10813,7 +10813,7 @@
         <v>2</v>
       </c>
       <c r="D581">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="582">
@@ -10885,7 +10885,7 @@
         <v>2</v>
       </c>
       <c r="D585">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="586">
@@ -11029,7 +11029,7 @@
         <v>2</v>
       </c>
       <c r="D593">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="594">
@@ -11299,7 +11299,7 @@
         <v>2</v>
       </c>
       <c r="D608">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="609">
@@ -11317,7 +11317,7 @@
         <v>2</v>
       </c>
       <c r="D609">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="610">
@@ -11353,7 +11353,7 @@
         <v>2</v>
       </c>
       <c r="D611">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="612">
@@ -11461,7 +11461,7 @@
         <v>2</v>
       </c>
       <c r="D617">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="618">
@@ -11551,7 +11551,7 @@
         <v>2</v>
       </c>
       <c r="D622">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="623">
@@ -11605,7 +11605,7 @@
         <v>2</v>
       </c>
       <c r="D625">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="626">
@@ -11767,7 +11767,7 @@
         <v>2</v>
       </c>
       <c r="D634">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="635">
@@ -11803,7 +11803,7 @@
         <v>2</v>
       </c>
       <c r="D636">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="637">
